--- a/data/obx_xlsx/AKVA.OL.xlsx
+++ b/data/obx_xlsx/AKVA.OL.xlsx
@@ -12155,16 +12155,37 @@
       <c r="O60" s="16">
         <v>45.76</v>
       </c>
-      <c r="P60" s="15"/>
+      <c r="P60" s="15">
+        <f>SUM(P61:P73)</f>
+        <v>41.94</v>
+      </c>
       <c r="Q60" s="16">
         <v>41.61</v>
       </c>
-      <c r="R60" s="15"/>
-      <c r="S60" s="15"/>
-      <c r="T60" s="15"/>
-      <c r="U60" s="15"/>
-      <c r="V60" s="15"/>
-      <c r="W60" s="15"/>
+      <c r="R60" s="15">
+        <f t="shared" ref="R60:W60" si="1">SUM(R61:R73)</f>
+        <v>39.07</v>
+      </c>
+      <c r="S60" s="15">
+        <f t="shared" si="1"/>
+        <v>41.51</v>
+      </c>
+      <c r="T60" s="15">
+        <f t="shared" si="1"/>
+        <v>33.99</v>
+      </c>
+      <c r="U60" s="15">
+        <f t="shared" si="1"/>
+        <v>22.31</v>
+      </c>
+      <c r="V60" s="15">
+        <f t="shared" si="1"/>
+        <v>5.49</v>
+      </c>
+      <c r="W60" s="15">
+        <f t="shared" si="1"/>
+        <v>4.18</v>
+      </c>
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="13" t="s">

--- a/data/obx_xlsx/AKVA.OL.xlsx
+++ b/data/obx_xlsx/AKVA.OL.xlsx
@@ -12992,15 +12992,9 @@
       <c r="F79" s="15"/>
       <c r="G79" s="15"/>
       <c r="H79" s="15"/>
-      <c r="I79" s="14">
-        <v>401.16</v>
-      </c>
-      <c r="J79" s="14">
-        <v>122.17</v>
-      </c>
-      <c r="K79" s="16">
-        <v>29.97</v>
-      </c>
+      <c r="I79" s="14"/>
+      <c r="J79" s="14"/>
+      <c r="K79" s="16"/>
       <c r="L79" s="16">
         <v>57.82</v>
       </c>
